--- a/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,0</t>
+          <t>2,5; 7,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,67</t>
+          <t>7,35; 13,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,5</t>
+          <t>6,13; 11,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,87</t>
+          <t>1,63; 7,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,23</t>
+          <t>6,8; 13,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,66</t>
+          <t>8,64; 14,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,18</t>
+          <t>2,7; 5,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 12,43</t>
+          <t>7,85; 12,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,72</t>
+          <t>8,09; 11,87</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,95</t>
+          <t>0,89; 4,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,46</t>
+          <t>7,66; 14,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,6</t>
+          <t>8,17; 14,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,84</t>
+          <t>2,97; 7,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,2</t>
+          <t>6,63; 12,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 16,19</t>
+          <t>9,96; 16,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,95</t>
+          <t>2,24; 4,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,59</t>
+          <t>7,96; 12,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,32</t>
+          <t>9,93; 14,34</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,8</t>
+          <t>2,48; 5,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,35</t>
+          <t>11,87; 18,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 11,07</t>
+          <t>2,2; 11,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,2</t>
+          <t>3,16; 8,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 14,7</t>
+          <t>4,87; 13,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,37; 18,42</t>
+          <t>9,63; 18,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,07</t>
+          <t>3,2; 5,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,67</t>
+          <t>10,73; 16,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 11,86</t>
+          <t>2,99; 11,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,95</t>
+          <t>3,47; 5,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,8</t>
+          <t>14,16; 18,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 14,83</t>
+          <t>9,84; 14,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,61</t>
+          <t>3,25; 6,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 17,98</t>
+          <t>13,06; 17,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,27</t>
+          <t>5,09; 12,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,81</t>
+          <t>3,79; 5,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,79</t>
+          <t>14,29; 17,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,76</t>
+          <t>6,91; 12,45</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,92</t>
+          <t>3,14; 6,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,83; 24,59</t>
+          <t>18,12; 24,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,44; 16,3</t>
+          <t>10,3; 16,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,52</t>
+          <t>2,76; 5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 20,41</t>
+          <t>14,64; 20,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,33; 40,06</t>
+          <t>9,44; 39,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,66</t>
+          <t>3,28; 5,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 21,59</t>
+          <t>17,02; 21,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 31,05</t>
+          <t>10,65; 30,26</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,57</t>
+          <t>1,87; 7,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,12; 20,8</t>
+          <t>12,24; 20,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 20,91</t>
+          <t>4,77; 19,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,79</t>
+          <t>3,43; 5,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 19,04</t>
+          <t>13,79; 18,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 12,83</t>
+          <t>8,2; 12,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,61</t>
+          <t>3,39; 5,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,26; 18,42</t>
+          <t>14,5; 18,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,23</t>
+          <t>8,25; 13,04</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,93</t>
+          <t>3,5; 4,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,04</t>
+          <t>14,36; 16,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,76</t>
+          <t>8,03; 11,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,28</t>
+          <t>3,79; 5,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,47; 15,89</t>
+          <t>13,42; 15,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,77; 19,02</t>
+          <t>9,69; 18,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,83</t>
+          <t>3,79; 4,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,19; 15,96</t>
+          <t>14,23; 16,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,19</t>
+          <t>9,7; 14,21</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11424; 30622</t>
+          <t>10946; 32041</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31095; 58650</t>
+          <t>31532; 57933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31335; 58109</t>
+          <t>30972; 57851</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5213; 21589</t>
+          <t>5125; 23036</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22932; 45922</t>
+          <t>23615; 46486</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38997; 65582</t>
+          <t>38641; 64362</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20085; 46421</t>
+          <t>20276; 44749</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59763; 96480</t>
+          <t>60918; 95881</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76268; 111637</t>
+          <t>77038; 113056</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3768; 16560</t>
+          <t>3711; 17042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29085; 54539</t>
+          <t>28897; 54034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36963; 66041</t>
+          <t>36949; 66596</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10135; 26488</t>
+          <t>10030; 26642</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24941; 49158</t>
+          <t>24671; 46270</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38559; 61953</t>
+          <t>38118; 63158</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16485; 37489</t>
+          <t>16967; 37334</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58869; 94364</t>
+          <t>59662; 93903</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82500; 119583</t>
+          <t>82922; 119699</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15867; 36501</t>
+          <t>15605; 36453</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62901; 95786</t>
+          <t>61948; 95650</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11850; 73983</t>
+          <t>14679; 75259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8901; 23925</t>
+          <t>8223; 22972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7796; 24418</t>
+          <t>8096; 22963</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15637; 30742</t>
+          <t>16069; 31514</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28817; 54002</t>
+          <t>28460; 52941</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76820; 114677</t>
+          <t>73813; 112529</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25027; 99011</t>
+          <t>24989; 96620</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40827; 68946</t>
+          <t>40220; 68845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165749; 216110</t>
+          <t>162825; 216215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104168; 153464</t>
+          <t>101861; 149642</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24560; 50699</t>
+          <t>24918; 51205</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106219; 148497</t>
+          <t>107843; 147801</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45702; 120017</t>
+          <t>49755; 119788</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72644; 111950</t>
+          <t>72957; 112115</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>283068; 351474</t>
+          <t>282206; 348972</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>153576; 256845</t>
+          <t>139085; 250554</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16105; 35322</t>
+          <t>16058; 35691</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>110699; 152629</t>
+          <t>112444; 153939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49586; 77418</t>
+          <t>48915; 79190</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19858; 42062</t>
+          <t>21023; 44081</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109135; 150697</t>
+          <t>108100; 152385</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78537; 337016</t>
+          <t>79463; 328806</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42347; 72029</t>
+          <t>41778; 72421</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>233659; 293407</t>
+          <t>231252; 293705</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>138805; 408785</t>
+          <t>140223; 398304</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5739; 20200</t>
+          <t>4981; 20214</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34813; 59740</t>
+          <t>35145; 59473</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12793; 50288</t>
+          <t>11470; 47585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36461; 64208</t>
+          <t>38074; 66304</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>153688; 206020</t>
+          <t>149233; 204334</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63258; 97712</t>
+          <t>62445; 96345</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47813; 77221</t>
+          <t>46698; 78268</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>195286; 252198</t>
+          <t>198539; 253560</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80897; 132552</t>
+          <t>82653; 130642</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>119482; 168572</t>
+          <t>119785; 169017</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>486038; 576785</t>
+          <t>486029; 570879</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275838; 397115</t>
+          <t>271081; 395938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>135471; 187346</t>
+          <t>134490; 186792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>475688; 561346</t>
+          <t>473840; 559848</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>349642; 680601</t>
+          <t>346688; 652182</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>269635; 336590</t>
+          <t>264551; 337564</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>981727; 1104254</t>
+          <t>984070; 1108861</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>677988; 986657</t>
+          <t>674378; 987825</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -51,34 +51,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -505,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,12 +485,6 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,67 +499,31 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -605,12 +535,6 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,47 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -678,47 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,33</t>
+          <t>7,17; 13,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 13,5</t>
+          <t>9,7; 15,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,45</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 7,33</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 13,39</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,64; 14,38</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,7; 5,95</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,85; 12,35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8,09; 11,87</t>
+          <t>9,09; 13,1</t>
         </is>
       </c>
     </row>
@@ -735,47 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -788,47 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,07</t>
+          <t>8,62; 15,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 14,32</t>
+          <t>10,46; 16,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,73</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2,97; 7,88</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,63; 12,43</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,96; 16,51</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,24; 4,93</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,96; 12,53</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9,93; 14,34</t>
+          <t>10,3; 14,66</t>
         </is>
       </c>
     </row>
@@ -845,47 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -898,47 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,79</t>
+          <t>7,64; 13,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 18,33</t>
+          <t>10,27; 19,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,26</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,16; 8,83</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,87; 13,82</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,63; 18,88</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,2; 5,95</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10,73; 16,36</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2,99; 11,57</t>
+          <t>9,03; 14,19</t>
         </is>
       </c>
     </row>
@@ -955,47 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,94</t>
+          <t>10,49; 15,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,16; 18,81</t>
+          <t>11,36; 15,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 14,46</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3,25; 6,68</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,06; 17,9</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,09; 12,25</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,79; 5,82</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14,29; 17,66</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6,91; 12,45</t>
+          <t>11,49; 14,65</t>
         </is>
       </c>
     </row>
@@ -1065,47 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,99</t>
+          <t>14,24; 20,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 24,8</t>
+          <t>9,8; 13,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,3; 16,67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 5,79</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,64; 20,64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,44; 39,08</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,28; 5,69</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17,02; 21,61</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10,65; 30,26</t>
+          <t>12,0; 15,63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1175,47 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,57</t>
+          <t>4,67; 19,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,24; 20,71</t>
+          <t>8,72; 12,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,77; 19,79</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3,43; 5,98</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>13,79; 18,88</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>8,2; 12,65</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>3,39; 5,69</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>14,5; 18,52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>8,25; 13,04</t>
+          <t>8,54; 12,83</t>
         </is>
       </c>
     </row>
@@ -1285,47 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,94</t>
+          <t>11,09; 13,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,86</t>
+          <t>11,21; 13,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,73</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3,79; 5,26</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,42; 15,85</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 18,23</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,79; 4,84</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>14,23; 16,03</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>9,7; 14,21</t>
+          <t>11,38; 13,02</t>
         </is>
       </c>
     </row>
@@ -1390,13 +894,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C1:E1"/>
+  <mergeCells count="8">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
@@ -1413,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1421,12 +922,6 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1441,67 +936,31 @@
           <t>Hombre</t>
         </is>
       </c>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1513,12 +972,6 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1533,45 +986,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>117</t>
         </is>
@@ -1586,47 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11648</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33393</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49973</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31055</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76843</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>93076</t>
+          <t>113244</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10946; 32041</t>
+          <t>39487; 71683</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31532; 57933</t>
+          <t>47352; 75028</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30972; 57851</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5125; 23036</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23615; 46486</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>38641; 64362</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20276; 44749</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>60918; 95881</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>77038; 113056</t>
+          <t>94453; 136135</t>
         </is>
       </c>
     </row>
@@ -1696,45 +1059,15 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
@@ -1749,47 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40870</t>
+          <t>55788</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16498</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34490</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49846</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24951</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>75360</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100132</t>
+          <t>111223</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3711; 17042</t>
+          <t>41656; 72528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28897; 54034</t>
+          <t>44252; 68976</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36949; 66596</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>10030; 26642</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>24671; 46270</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>38118; 63158</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>16967; 37334</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>59662; 93903</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82922; 119699</t>
+          <t>93394; 132887</t>
         </is>
       </c>
     </row>
@@ -1859,45 +1132,15 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
@@ -1912,47 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78956</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15251</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14291</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22171</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39751</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>93246</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65065</t>
+          <t>75575</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15605; 36453</t>
+          <t>36041; 64202</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61948; 95650</t>
+          <t>19258; 36007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14679; 75259</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8223; 22972</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8096; 22963</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16069; 31514</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28460; 52941</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>73813; 112529</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24989; 96620</t>
+          <t>59544; 93511</t>
         </is>
       </c>
     </row>
@@ -2022,45 +1205,15 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>286</t>
         </is>
@@ -2075,47 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>54062</t>
+          <t>142499</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>187940</t>
+          <t>113731</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123577</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35904</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>126230</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89999</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89966</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>314170</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>213576</t>
+          <t>256230</t>
         </is>
       </c>
     </row>
@@ -2128,47 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40220; 68845</t>
+          <t>118780; 170834</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162825; 216215</t>
+          <t>97806; 132830</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101861; 149642</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>24918; 51205</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>107843; 147801</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>49755; 119788</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>72957; 112115</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>282206; 348972</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>139085; 250554</t>
+          <t>228949; 291976</t>
         </is>
       </c>
     </row>
@@ -2185,45 +1278,15 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>227</t>
         </is>
@@ -2238,47 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24931</t>
+          <t>97552</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>131947</t>
+          <t>96767</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30402</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>129549</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>146525</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>55333</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>261495</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>209348</t>
+          <t>194319</t>
         </is>
       </c>
     </row>
@@ -2291,54 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16058; 35691</t>
+          <t>80886; 116548</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>112444; 153939</t>
+          <t>81388; 111712</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48915; 79190</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>21023; 44081</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>108100; 152385</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>79463; 328806</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>41778; 72421</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>231252; 293705</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>140223; 398304</t>
+          <t>167860; 218643</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2353,40 +1356,10 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>127</t>
         </is>
@@ -2401,47 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46045</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>49872</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>176842</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>76916</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>60636</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>222887</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>102562</t>
+          <t>113213</t>
         </is>
       </c>
     </row>
@@ -2454,47 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4981; 20214</t>
+          <t>11075; 45067</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35145; 59473</t>
+          <t>73615; 108184</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11470; 47585</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38074; 66304</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>149233; 204334</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>62445; 96345</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>46698; 78268</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>198539; 253560</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>82653; 130642</t>
+          <t>92353; 138725</t>
         </is>
       </c>
     </row>
@@ -2511,45 +1424,15 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>361</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>599</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>960</t>
         </is>
@@ -2564,47 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>142116</t>
+          <t>421360</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>529206</t>
+          <t>442443</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>348329</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>159575</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>514794</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>435431</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>301691</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1044001</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>783760</t>
+          <t>863804</t>
         </is>
       </c>
     </row>
@@ -2617,47 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>119785; 169017</t>
+          <t>381666; 465045</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>486029; 570879</t>
+          <t>407623; 481198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>271081; 395938</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>134490; 186792</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>473840; 559848</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>346688; 652182</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>264551; 337564</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>984070; 1108861</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>674378; 987825</t>
+          <t>805185; 921426</t>
         </is>
       </c>
     </row>
@@ -2669,14 +1492,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C1:E1"/>
+  <mergeCells count="8">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>

--- a/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,02</t>
+          <t>36,29; 44,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,7; 15,36</t>
+          <t>31,67; 39,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 13,1</t>
+          <t>35,05; 40,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 15,01</t>
+          <t>32,31; 41,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 16,3</t>
+          <t>35,85; 43,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,66</t>
+          <t>35,02; 41,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 13,61</t>
+          <t>32,94; 42,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 19,2</t>
+          <t>36,2; 48,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 14,19</t>
+          <t>35,03; 42,49</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,09</t>
+          <t>35,54; 41,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,42</t>
+          <t>32,29; 38,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 14,65</t>
+          <t>34,72; 39,27</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,52</t>
+          <t>36,91; 46,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,45</t>
+          <t>45,72; 51,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 15,63</t>
+          <t>43,26; 48,5</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 19,0</t>
+          <t>30,29; 48,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,81</t>
+          <t>40,67; 47,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,83</t>
+          <t>39,16; 46,13</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 13,51</t>
+          <t>37,15; 40,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,24</t>
+          <t>39,59; 42,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,38; 13,02</t>
+          <t>39,0; 41,22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -986,17 +986,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>454</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53468</t>
+          <t>221823</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59775</t>
+          <t>171802</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113244</t>
+          <t>393625</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39487; 71683</t>
+          <t>199261; 246263</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47352; 75028</t>
+          <t>154434; 190850</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94453; 136135</t>
+          <t>363379; 424963</t>
         </is>
       </c>
     </row>
@@ -1059,17 +1059,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>177</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>404</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>176520</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55788</t>
+          <t>167259</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>343779</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41656; 72528</t>
+          <t>155867; 199936</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44252; 68976</t>
+          <t>151694; 185446</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93394; 132887</t>
+          <t>317176; 372206</t>
         </is>
       </c>
     </row>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>190</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48685</t>
+          <t>177322</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26890</t>
+          <t>77924</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75575</t>
+          <t>255246</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36041; 64202</t>
+          <t>155339; 198808</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19258; 36007</t>
+          <t>67620; 90094</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59544; 93511</t>
+          <t>230647; 279740</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1205,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>428</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>828</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>142499</t>
+          <t>434441</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>113731</t>
+          <t>302805</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256230</t>
+          <t>737246</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>118780; 170834</t>
+          <t>402304; 471553</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97806; 132830</t>
+          <t>277800; 328049</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>228949; 291976</t>
+          <t>691652; 782247</t>
         </is>
       </c>
     </row>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>237</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>578</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>815</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>97552</t>
+          <t>237434</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96767</t>
+          <t>404002</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194319</t>
+          <t>641436</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>80886; 116548</t>
+          <t>209262; 262300</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81388; 111712</t>
+          <t>379554; 429608</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167860; 218643</t>
+          <t>604284; 677558</t>
         </is>
       </c>
     </row>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>526</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>91658</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>89492</t>
+          <t>369987</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113213</t>
+          <t>461646</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11075; 45067</t>
+          <t>71347; 115162</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73615; 108184</t>
+          <t>343365; 397595</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92353; 138725</t>
+          <t>422919; 498145</t>
         </is>
       </c>
     </row>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>3331</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>421360</t>
+          <t>1339198</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>442443</t>
+          <t>1493781</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>863804</t>
+          <t>2832978</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>381666; 465045</t>
+          <t>1277003; 1404699</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>407623; 481198</t>
+          <t>1438058; 1549822</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>805185; 921426</t>
+          <t>2757093; 2914363</t>
         </is>
       </c>
     </row>
